--- a/data/Caffeine/shen2019/shen2019_caffeine_time_trial_endurance.xlsx
+++ b/data/Caffeine/shen2019/shen2019_caffeine_time_trial_endurance.xlsx
@@ -230,7 +230,7 @@
     <t>notes</t>
   </si>
   <si>
-    <t>d used - could not get sample sizes</t>
+    <t>n not available, d used</t>
   </si>
 </sst>
 </file>
